--- a/Map Opeperation/tb_de_para.xlsx
+++ b/Map Opeperation/tb_de_para.xlsx
@@ -1,22 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perna\Desktop\STALLANTIS\Volume_Accuracy\Map Opeperation\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2AB39A-C7EA-47DD-BEE4-92E03583E122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Coded"/>
-    <sheet r:id="rId2" sheetId="2" name="Updated"/>
-    <sheet r:id="rId3" sheetId="3" name="tb_de_para"/>
+    <sheet name="Coded" sheetId="1" r:id="rId1"/>
+    <sheet name="Updated" sheetId="2" r:id="rId2"/>
+    <sheet name="tb_de_para" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Coded!$A$1:$E$93</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2996" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2999" uniqueCount="291">
   <si>
     <t>Multivalues</t>
   </si>
@@ -886,13 +908,15 @@
   </si>
   <si>
     <t>Superturbo</t>
+  </si>
+  <si>
+    <t>Cilindrada (l)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -915,7 +939,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -933,7 +957,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFf2f2f2"/>
+      <color rgb="FFF2F2F2"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -952,7 +976,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF10253f"/>
+        <fgColor rgb="FF10253F"/>
       </patternFill>
     </fill>
     <fill>
@@ -1001,16 +1025,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1026,61 +1050,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1091,10 +1108,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1132,71 +1149,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1224,7 +1241,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1247,11 +1264,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1260,13 +1277,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1276,7 +1293,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1285,7 +1302,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1294,7 +1311,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1302,10 +1319,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1370,21 +1387,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E94"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="3" width="12.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="35.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="28.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="15" width="33.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="15" width="37.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="12.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.7265625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.7265625" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
+    <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>212</v>
       </c>
@@ -1401,7 +1418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>213</v>
       </c>
@@ -1418,7 +1435,7 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>136</v>
       </c>
@@ -1435,7 +1452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>214</v>
       </c>
@@ -1452,7 +1469,7 @@
         <v>215</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>141</v>
       </c>
@@ -1469,7 +1486,7 @@
         <v>216</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>217</v>
       </c>
@@ -1486,7 +1503,7 @@
         <v>219</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row r="7" spans="1:5" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>220</v>
       </c>
@@ -1503,7 +1520,7 @@
         <v>127</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+    <row r="8" spans="1:5" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>143</v>
       </c>
@@ -1520,7 +1537,7 @@
         <v>96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row r="9" spans="1:5" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>221</v>
       </c>
@@ -1537,7 +1554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    <row r="10" spans="1:5" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>147</v>
       </c>
@@ -1554,7 +1571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    <row r="11" spans="1:5" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
@@ -1571,7 +1588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row r="12" spans="1:5" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>148</v>
       </c>
@@ -1588,7 +1605,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    <row r="13" spans="1:5" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>149</v>
       </c>
@@ -1605,7 +1622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>150</v>
       </c>
@@ -1620,7 +1637,7 @@
       </c>
       <c r="E14" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>223</v>
       </c>
@@ -1635,7 +1652,7 @@
       </c>
       <c r="E15" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>152</v>
       </c>
@@ -1650,7 +1667,7 @@
       </c>
       <c r="E16" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row r="17" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>224</v>
       </c>
@@ -1667,7 +1684,7 @@
         <v>227</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>228</v>
       </c>
@@ -1684,7 +1701,7 @@
         <v>227</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>229</v>
       </c>
@@ -1701,7 +1718,7 @@
         <v>230</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>231</v>
       </c>
@@ -1718,7 +1735,7 @@
         <v>230</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>232</v>
       </c>
@@ -1735,7 +1752,7 @@
         <v>233</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>234</v>
       </c>
@@ -1752,7 +1769,7 @@
         <v>233</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>235</v>
       </c>
@@ -1769,7 +1786,7 @@
         <v>236</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>237</v>
       </c>
@@ -1786,7 +1803,7 @@
         <v>236</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>238</v>
       </c>
@@ -1803,7 +1820,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>239</v>
       </c>
@@ -1820,7 +1837,7 @@
         <v>69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>240</v>
       </c>
@@ -1837,7 +1854,7 @@
         <v>241</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row r="28" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>242</v>
       </c>
@@ -1854,7 +1871,7 @@
         <v>241</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>243</v>
       </c>
@@ -1871,7 +1888,7 @@
         <v>244</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row r="30" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>245</v>
       </c>
@@ -1888,7 +1905,7 @@
         <v>246</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row r="31" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>247</v>
       </c>
@@ -1905,7 +1922,7 @@
         <v>98</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row r="32" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>153</v>
       </c>
@@ -1922,7 +1939,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row r="33" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>154</v>
       </c>
@@ -1939,7 +1956,7 @@
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row r="34" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>155</v>
       </c>
@@ -1956,7 +1973,7 @@
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row r="35" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>156</v>
       </c>
@@ -1973,7 +1990,7 @@
         <v>96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row r="36" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>157</v>
       </c>
@@ -1990,7 +2007,7 @@
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>153</v>
       </c>
@@ -2007,7 +2024,7 @@
         <v>248</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row r="38" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>158</v>
       </c>
@@ -2024,7 +2041,7 @@
         <v>249</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row r="39" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>250</v>
       </c>
@@ -2041,7 +2058,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row r="40" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>253</v>
       </c>
@@ -2058,7 +2075,7 @@
         <v>255</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row r="41" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>159</v>
       </c>
@@ -2075,7 +2092,7 @@
         <v>257</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row r="42" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>160</v>
       </c>
@@ -2092,7 +2109,7 @@
         <v>258</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row r="43" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>161</v>
       </c>
@@ -2109,7 +2126,7 @@
         <v>260</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>162</v>
       </c>
@@ -2126,7 +2143,7 @@
         <v>261</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row r="45" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>163</v>
       </c>
@@ -2143,7 +2160,7 @@
         <v>263</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row r="46" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>164</v>
       </c>
@@ -2160,7 +2177,7 @@
         <v>265</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row r="47" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>266</v>
       </c>
@@ -2177,7 +2194,7 @@
         <v>267</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row r="48" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>165</v>
       </c>
@@ -2194,7 +2211,7 @@
         <v>268</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row r="49" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>166</v>
       </c>
@@ -2211,7 +2228,7 @@
         <v>269</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row r="50" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>167</v>
       </c>
@@ -2228,7 +2245,7 @@
         <v>270</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row r="51" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>168</v>
       </c>
@@ -2245,7 +2262,7 @@
         <v>271</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row r="52" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>169</v>
       </c>
@@ -2262,7 +2279,7 @@
         <v>77</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row r="53" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>170</v>
       </c>
@@ -2279,7 +2296,7 @@
         <v>86</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row r="54" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>171</v>
       </c>
@@ -2296,7 +2313,7 @@
         <v>109</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+    <row r="55" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>172</v>
       </c>
@@ -2313,7 +2330,7 @@
         <v>272</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row r="56" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>173</v>
       </c>
@@ -2330,7 +2347,7 @@
         <v>274</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row r="57" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>174</v>
       </c>
@@ -2347,7 +2364,7 @@
         <v>275</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row r="58" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>276</v>
       </c>
@@ -2364,7 +2381,7 @@
         <v>279</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row r="59" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>280</v>
       </c>
@@ -2381,7 +2398,7 @@
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+    <row r="60" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>177</v>
       </c>
@@ -2398,7 +2415,7 @@
         <v>64</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row r="61" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>178</v>
       </c>
@@ -2415,7 +2432,7 @@
         <v>96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+    <row r="62" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>179</v>
       </c>
@@ -2432,7 +2449,7 @@
         <v>281</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+    <row r="63" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>180</v>
       </c>
@@ -2449,7 +2466,7 @@
         <v>281</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row r="64" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>181</v>
       </c>
@@ -2466,7 +2483,7 @@
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row r="65" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>182</v>
       </c>
@@ -2483,7 +2500,7 @@
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row r="66" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>183</v>
       </c>
@@ -2500,7 +2517,7 @@
         <v>96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row r="67" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>184</v>
       </c>
@@ -2517,7 +2534,7 @@
         <v>96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row r="68" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>185</v>
       </c>
@@ -2534,7 +2551,7 @@
         <v>64</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+    <row r="69" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>186</v>
       </c>
@@ -2551,7 +2568,7 @@
         <v>282</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row r="70" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>187</v>
       </c>
@@ -2568,7 +2585,7 @@
         <v>282</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row r="71" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>188</v>
       </c>
@@ -2585,7 +2602,7 @@
         <v>283</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row r="72" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>189</v>
       </c>
@@ -2602,7 +2619,7 @@
         <v>283</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row r="73" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>190</v>
       </c>
@@ -2619,7 +2636,7 @@
         <v>283</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row r="74" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>284</v>
       </c>
@@ -2636,7 +2653,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row r="75" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>191</v>
       </c>
@@ -2653,7 +2670,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row r="76" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>192</v>
       </c>
@@ -2670,7 +2687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row r="77" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>193</v>
       </c>
@@ -2687,7 +2704,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row r="78" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>194</v>
       </c>
@@ -2704,7 +2721,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row r="79" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>195</v>
       </c>
@@ -2721,7 +2738,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row r="80" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>196</v>
       </c>
@@ -2738,7 +2755,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row r="81" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>197</v>
       </c>
@@ -2755,7 +2772,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row r="82" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>198</v>
       </c>
@@ -2772,7 +2789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+    <row r="83" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>199</v>
       </c>
@@ -2783,13 +2800,13 @@
         <v>12</v>
       </c>
       <c r="D83" s="14">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E83" s="14">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>285</v>
       </c>
@@ -2806,7 +2823,7 @@
         <v>286</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+    <row r="85" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>203</v>
       </c>
@@ -2823,7 +2840,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+    <row r="86" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>204</v>
       </c>
@@ -2840,7 +2857,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+    <row r="87" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>205</v>
       </c>
@@ -2857,7 +2874,7 @@
         <v>120</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+    <row r="88" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>206</v>
       </c>
@@ -2874,7 +2891,7 @@
         <v>120</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+    <row r="89" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>207</v>
       </c>
@@ -2891,7 +2908,7 @@
         <v>287</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+    <row r="90" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>288</v>
       </c>
@@ -2908,7 +2925,7 @@
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+    <row r="91" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>208</v>
       </c>
@@ -2925,7 +2942,7 @@
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+    <row r="92" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>209</v>
       </c>
@@ -2942,7 +2959,7 @@
         <v>289</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+    <row r="93" spans="1:5" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>210</v>
       </c>
@@ -2959,43 +2976,52 @@
         <v>289</v>
       </c>
     </row>
+    <row r="94" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" s="14">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E94" s="14">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E93" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="CC(2.2)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:U109"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="3" width="21.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="3" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="3" width="23.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="3" width="21.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="16" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3030,9 +3056,10 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5">
+    <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q2))</f>
+        <v>TT(4X2)</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>136</v>
@@ -3065,9 +3092,10 @@
       </c>
       <c r="U2" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5">
+    <row r="3" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q3))</f>
+        <v>TT(4X2)</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>136</v>
@@ -3100,9 +3128,10 @@
       </c>
       <c r="U3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5">
+    <row r="4" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q4))</f>
+        <v>TT(4X2)</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>136</v>
@@ -3135,9 +3164,10 @@
       </c>
       <c r="U4" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="5">
+    <row r="5" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q5))</f>
+        <v>TT(4X2)</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>136</v>
@@ -3170,9 +3200,10 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="5">
+    <row r="6" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q6))</f>
+        <v>TT(4X2)</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>136</v>
@@ -3205,9 +3236,10 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="5">
+    <row r="7" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q7))</f>
+        <v>TT(4X2)</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>136</v>
@@ -3240,9 +3272,10 @@
         <v>117</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="5">
+    <row r="8" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q8))</f>
+        <v>ELT(BSG12)</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>141</v>
@@ -3275,9 +3308,10 @@
       </c>
       <c r="U8" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="5">
+    <row r="9" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q9))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>143</v>
@@ -3310,9 +3344,10 @@
       </c>
       <c r="U9" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="5">
+    <row r="10" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q10))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>143</v>
@@ -3345,9 +3380,10 @@
       </c>
       <c r="U10" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="5">
+    <row r="11" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q11))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>143</v>
@@ -3380,9 +3416,10 @@
       </c>
       <c r="U11" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="5">
+    <row r="12" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q12))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>143</v>
@@ -3415,9 +3452,10 @@
       </c>
       <c r="U12" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="5">
+    <row r="13" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q13))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>143</v>
@@ -3450,9 +3488,10 @@
       </c>
       <c r="U13" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="5">
+    <row r="14" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q14))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>143</v>
@@ -3485,9 +3524,10 @@
       </c>
       <c r="U14" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="5">
+    <row r="15" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q15))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>143</v>
@@ -3520,9 +3560,10 @@
       </c>
       <c r="U15" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="5">
+    <row r="16" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q16))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>143</v>
@@ -3555,9 +3596,10 @@
       </c>
       <c r="U16" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="5">
+    <row r="17" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q17))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>143</v>
@@ -3590,9 +3632,10 @@
       </c>
       <c r="U17" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="5">
+    <row r="18" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q18))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>143</v>
@@ -3625,9 +3668,10 @@
         <v>104</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="5">
+    <row r="19" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q19))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>143</v>
@@ -3660,9 +3704,10 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="5">
+    <row r="20" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q20))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>143</v>
@@ -3695,9 +3740,10 @@
         <v>115</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="5">
+    <row r="21" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q21))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>143</v>
@@ -3730,9 +3776,10 @@
         <v>127</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="5">
+    <row r="22" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q22))</f>
+        <v>KW(125)</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>143</v>
@@ -3765,9 +3812,10 @@
         <v>126</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="5">
+    <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q23))</f>
+        <v>TC(PKDC)</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>147</v>
@@ -3800,9 +3848,10 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="5">
+    <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q24))</f>
+        <v>TC(PKDC)</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>147</v>
@@ -3835,9 +3884,10 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="5">
+    <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q25))</f>
+        <v>VLE(6)</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>148</v>
@@ -3874,9 +3924,10 @@
       </c>
       <c r="U25" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="5">
+    <row r="26" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q26))</f>
+        <v>VLE(6)</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>148</v>
@@ -3913,9 +3964,10 @@
       </c>
       <c r="U26" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="5">
+    <row r="27" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q27))</f>
+        <v>VLE(6)</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>148</v>
@@ -3952,9 +4004,10 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="5">
+    <row r="28" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q28))</f>
+        <v>VLE(6)</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>148</v>
@@ -3991,9 +4044,10 @@
       </c>
       <c r="U28" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="5">
+    <row r="29" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q29))</f>
+        <v>VLE(6)</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>148</v>
@@ -4030,9 +4084,10 @@
       </c>
       <c r="U29" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="5">
+    <row r="30" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q30))</f>
+        <v>VLE(6)</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>148</v>
@@ -4069,9 +4124,10 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="5">
+    <row r="31" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q31))</f>
+        <v>NP(2)</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>152</v>
@@ -4104,9 +4160,10 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="5">
+    <row r="32" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q32))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>153</v>
@@ -4163,9 +4220,10 @@
       </c>
       <c r="U32" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="5">
+    <row r="33" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q33))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>153</v>
@@ -4222,9 +4280,10 @@
       </c>
       <c r="U33" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="5">
+    <row r="34" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q34))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>153</v>
@@ -4281,9 +4340,10 @@
       </c>
       <c r="U34" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="5">
+    <row r="35" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q35))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>153</v>
@@ -4340,9 +4400,10 @@
       </c>
       <c r="U35" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="5">
+    <row r="36" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q36))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>153</v>
@@ -4399,9 +4460,10 @@
       </c>
       <c r="U36" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="5">
+    <row r="37" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q37))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>153</v>
@@ -4458,9 +4520,10 @@
       </c>
       <c r="U37" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="5">
+    <row r="38" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q38))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>153</v>
@@ -4517,9 +4580,10 @@
       </c>
       <c r="U38" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="5">
+    <row r="39" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q39))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>153</v>
@@ -4576,9 +4640,10 @@
       </c>
       <c r="U39" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="5">
+    <row r="40" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q40))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>153</v>
@@ -4635,9 +4700,10 @@
       </c>
       <c r="U40" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="5">
+    <row r="41" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q41))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>153</v>
@@ -4694,9 +4760,10 @@
         <v>98</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="5">
+    <row r="42" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q42))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>153</v>
@@ -4753,9 +4820,10 @@
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="5">
+    <row r="43" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q43))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>153</v>
@@ -4812,9 +4880,10 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="5">
+    <row r="44" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q44))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>153</v>
@@ -4871,9 +4940,10 @@
         <v>118</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="5">
+    <row r="45" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q45))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>153</v>
@@ -4930,9 +5000,10 @@
         <v>119</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="5">
+    <row r="46" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q46))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>153</v>
@@ -4989,9 +5060,10 @@
         <v>132</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="5">
+    <row r="47" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q47))</f>
+        <v>ECO(BPL8)</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>153</v>
@@ -5048,9 +5120,10 @@
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="5">
+    <row r="48" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q48))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>165</v>
@@ -5101,9 +5174,10 @@
       </c>
       <c r="U48" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="5">
+    <row r="49" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q49))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>165</v>
@@ -5154,9 +5228,10 @@
       </c>
       <c r="U49" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="5">
+    <row r="50" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q50))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>165</v>
@@ -5207,9 +5282,10 @@
       </c>
       <c r="U50" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="5">
+    <row r="51" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q51))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>165</v>
@@ -5260,9 +5336,10 @@
       </c>
       <c r="U51" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="5">
+    <row r="52" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q52))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>165</v>
@@ -5313,9 +5390,10 @@
       </c>
       <c r="U52" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="5">
+    <row r="53" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q53))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>165</v>
@@ -5366,9 +5444,10 @@
       </c>
       <c r="U53" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
-      <c r="A54" s="5">
+    <row r="54" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q54))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>165</v>
@@ -5419,9 +5498,10 @@
       </c>
       <c r="U54" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="5">
+    <row r="55" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q55))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>165</v>
@@ -5472,9 +5552,10 @@
       </c>
       <c r="U55" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
-      <c r="A56" s="5">
+    <row r="56" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q56))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>165</v>
@@ -5525,9 +5606,10 @@
       </c>
       <c r="U56" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
-      <c r="A57" s="5">
+    <row r="57" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q57))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>165</v>
@@ -5578,9 +5660,10 @@
       </c>
       <c r="U57" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
-      <c r="A58" s="5">
+    <row r="58" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q58))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>165</v>
@@ -5631,9 +5714,10 @@
       </c>
       <c r="U58" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
-      <c r="A59" s="5">
+    <row r="59" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q59))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>165</v>
@@ -5684,9 +5768,10 @@
       </c>
       <c r="U59" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="5">
+    <row r="60" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q60))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>165</v>
@@ -5737,9 +5822,10 @@
       </c>
       <c r="U60" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="5">
+    <row r="61" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q61))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>165</v>
@@ -5790,9 +5876,10 @@
       </c>
       <c r="U61" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="5">
+    <row r="62" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q62))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>165</v>
@@ -5843,9 +5930,10 @@
       </c>
       <c r="U62" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="5">
+    <row r="63" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q63))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>165</v>
@@ -5896,9 +5984,10 @@
       </c>
       <c r="U63" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="5">
+    <row r="64" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q64))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>165</v>
@@ -5949,9 +6038,10 @@
         <v>112</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="5">
+    <row r="65" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q65))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>165</v>
@@ -6002,9 +6092,10 @@
         <v>114</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="5">
+    <row r="66" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q66))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>165</v>
@@ -6055,9 +6146,10 @@
         <v>109</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
-      <c r="A67" s="5">
+    <row r="67" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q67))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>165</v>
@@ -6108,9 +6200,10 @@
         <v>108</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
-      <c r="A68" s="5">
+    <row r="68" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q68))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>165</v>
@@ -6161,9 +6254,10 @@
         <v>111</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
-      <c r="A69" s="5">
+    <row r="69" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q69))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>165</v>
@@ -6214,9 +6308,10 @@
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="5">
+    <row r="70" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q70))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>165</v>
@@ -6267,9 +6362,10 @@
         <v>113</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="5">
+    <row r="71" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q71))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>165</v>
@@ -6320,9 +6416,10 @@
         <v>124</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="5">
+    <row r="72" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q72))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>165</v>
@@ -6373,9 +6470,10 @@
         <v>122</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="5">
+    <row r="73" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q73))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>165</v>
@@ -6426,9 +6524,10 @@
         <v>123</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="5">
+    <row r="74" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q74))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>165</v>
@@ -6479,9 +6578,10 @@
         <v>121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
-      <c r="A75" s="5">
+    <row r="75" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q75))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>165</v>
@@ -6532,9 +6632,10 @@
         <v>129</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
-      <c r="A76" s="5">
+    <row r="76" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q76))</f>
+        <v>L(L11)</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>165</v>
@@ -6585,9 +6686,10 @@
         <v>130</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
-      <c r="A77" s="5">
+    <row r="77" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q77))</f>
+        <v>C513)</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>177</v>
@@ -6646,9 +6748,10 @@
       </c>
       <c r="U77" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="5">
+    <row r="78" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q78))</f>
+        <v>C513)</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>177</v>
@@ -6707,9 +6810,10 @@
       </c>
       <c r="U78" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="5">
+    <row r="79" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q79))</f>
+        <v>C513)</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>177</v>
@@ -6768,9 +6872,10 @@
       </c>
       <c r="U79" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
-      <c r="A80" s="5">
+    <row r="80" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q80))</f>
+        <v>C513)</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>177</v>
@@ -6829,9 +6934,10 @@
       </c>
       <c r="U80" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="5">
+    <row r="81" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q81))</f>
+        <v>C513)</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>177</v>
@@ -6890,9 +6996,10 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="5">
+    <row r="82" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q82))</f>
+        <v>C513)</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>177</v>
@@ -6951,9 +7058,10 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
-      <c r="A83" s="5">
+    <row r="83" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q83))</f>
+        <v>CC(1.6)</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>191</v>
@@ -7002,9 +7110,10 @@
       </c>
       <c r="U83" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
-      <c r="A84" s="5">
+    <row r="84" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q84))</f>
+        <v>CC(1.6)</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>191</v>
@@ -7053,9 +7162,10 @@
       </c>
       <c r="U84" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
-      <c r="A85" s="5">
+    <row r="85" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q85))</f>
+        <v>CC(1.6)</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>191</v>
@@ -7104,9 +7214,10 @@
       </c>
       <c r="U85" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
-      <c r="A86" s="5">
+    <row r="86" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q86))</f>
+        <v>CC(1.6)</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>191</v>
@@ -7155,9 +7266,10 @@
       </c>
       <c r="U86" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
-      <c r="A87" s="5">
+    <row r="87" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q87))</f>
+        <v>CC(1.6)</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>191</v>
@@ -7206,9 +7318,10 @@
         <v>200</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
-      <c r="A88" s="5">
+    <row r="88" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q88))</f>
+        <v>CC(1.6)</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>191</v>
@@ -7257,9 +7370,10 @@
         <v>49</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
-      <c r="A89" s="5">
+    <row r="89" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q89))</f>
+        <v>CC(1.6)</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>191</v>
@@ -7308,9 +7422,10 @@
         <v>201</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
-      <c r="A90" s="5">
+    <row r="90" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q90))</f>
+        <v>CMB(ALC)</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>203</v>
@@ -7351,9 +7466,10 @@
       </c>
       <c r="U90" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
-      <c r="A91" s="5">
+    <row r="91" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q91))</f>
+        <v>CMB(ALC)</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>203</v>
@@ -7394,9 +7510,10 @@
       </c>
       <c r="U91" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
-      <c r="A92" s="5">
+    <row r="92" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q92))</f>
+        <v>CMB(ALC)</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>203</v>
@@ -7437,9 +7554,10 @@
       </c>
       <c r="U92" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
-      <c r="A93" s="5">
+    <row r="93" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q93))</f>
+        <v>CMB(ALC)</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>203</v>
@@ -7480,9 +7598,10 @@
       </c>
       <c r="U93" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="5">
+    <row r="94" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q94))</f>
+        <v>CMB(ALC)</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>203</v>
@@ -7523,9 +7642,10 @@
       </c>
       <c r="U94" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
-      <c r="A95" s="5">
+    <row r="95" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q95))</f>
+        <v>CMB(ALC)</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>203</v>
@@ -7566,9 +7686,10 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
-      <c r="A96" s="5">
+    <row r="96" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q96))</f>
+        <v>CMB(ALC)</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>203</v>
@@ -7609,9 +7730,10 @@
         <v>107</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
-      <c r="A97" s="5">
+    <row r="97" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q97))</f>
+        <v>CMB(ALC)</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>203</v>
@@ -7652,9 +7774,10 @@
         <v>120</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
-      <c r="A98" s="5">
+    <row r="98" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q98))</f>
+        <v>CMB(ALC)</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>203</v>
@@ -7695,9 +7818,10 @@
         <v>128</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
-      <c r="A99" s="5">
+    <row r="99" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q99))</f>
+        <v>T(ASP)</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>208</v>
@@ -7734,9 +7858,10 @@
       </c>
       <c r="U99" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
-      <c r="A100" s="5">
+    <row r="100" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q100))</f>
+        <v>T(ASP)</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>208</v>
@@ -7773,9 +7898,10 @@
       </c>
       <c r="U100" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
-      <c r="A101" s="5">
+    <row r="101" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q101))</f>
+        <v>T(ASP)</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>208</v>
@@ -7812,9 +7938,10 @@
       </c>
       <c r="U101" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
-      <c r="A102" s="5">
+    <row r="102" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="5" t="str">
         <f>TRANSPOSE(_xlfn._xlws.FILTER(Coded!A:A,Coded!B:B=Updated!Q102))</f>
+        <v>T(ASP)</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>208</v>
@@ -7851,7 +7978,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+    <row r="103" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -7874,7 +8001,7 @@
       <c r="T103" s="2"/>
       <c r="U103" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
+    <row r="104" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -7897,7 +8024,7 @@
       <c r="T104" s="2"/>
       <c r="U104" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
+    <row r="105" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -7920,7 +8047,7 @@
       <c r="T105" s="2"/>
       <c r="U105" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
+    <row r="106" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -7943,7 +8070,7 @@
       <c r="T106" s="2"/>
       <c r="U106" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
+    <row r="107" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -7966,7 +8093,7 @@
       <c r="T107" s="2"/>
       <c r="U107" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
+    <row r="108" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -7989,7 +8116,7 @@
       <c r="T108" s="2"/>
       <c r="U108" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
+    <row r="109" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -8020,22 +8147,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F283"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="6" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8055,7 +8177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -8073,7 +8195,7 @@
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -8091,7 +8213,7 @@
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -8109,7 +8231,7 @@
       </c>
       <c r="F4" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -8127,7 +8249,7 @@
       </c>
       <c r="F5" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -8145,7 +8267,7 @@
       </c>
       <c r="F6" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -8163,7 +8285,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -8181,7 +8303,7 @@
       </c>
       <c r="F8" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -8199,7 +8321,7 @@
       </c>
       <c r="F9" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -8217,7 +8339,7 @@
       </c>
       <c r="F10" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
@@ -8235,7 +8357,7 @@
       </c>
       <c r="F11" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
@@ -8253,7 +8375,7 @@
       </c>
       <c r="F12" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -8271,7 +8393,7 @@
       </c>
       <c r="F13" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>35</v>
       </c>
@@ -8289,7 +8411,7 @@
       </c>
       <c r="F14" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -8307,7 +8429,7 @@
       </c>
       <c r="F15" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>37</v>
       </c>
@@ -8325,7 +8447,7 @@
       </c>
       <c r="F16" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>40</v>
       </c>
@@ -8343,7 +8465,7 @@
       </c>
       <c r="F17" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>41</v>
       </c>
@@ -8361,7 +8483,7 @@
       </c>
       <c r="F18" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
@@ -8379,7 +8501,7 @@
       </c>
       <c r="F19" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>43</v>
       </c>
@@ -8397,7 +8519,7 @@
       </c>
       <c r="F20" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>44</v>
       </c>
@@ -8415,7 +8537,7 @@
       </c>
       <c r="F21" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>45</v>
       </c>
@@ -8433,7 +8555,7 @@
       </c>
       <c r="F22" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
@@ -8451,7 +8573,7 @@
       </c>
       <c r="F23" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -8469,7 +8591,7 @@
       </c>
       <c r="F24" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>49</v>
       </c>
@@ -8487,7 +8609,7 @@
       </c>
       <c r="F25" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>52</v>
       </c>
@@ -8505,7 +8627,7 @@
       </c>
       <c r="F26" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>53</v>
       </c>
@@ -8523,7 +8645,7 @@
       </c>
       <c r="F27" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
@@ -8541,7 +8663,7 @@
       </c>
       <c r="F28" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
@@ -8559,7 +8681,7 @@
       </c>
       <c r="F29" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>57</v>
       </c>
@@ -8577,7 +8699,7 @@
       </c>
       <c r="F30" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>24</v>
       </c>
@@ -8595,7 +8717,7 @@
       </c>
       <c r="F31" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>58</v>
       </c>
@@ -8613,7 +8735,7 @@
       </c>
       <c r="F32" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>59</v>
       </c>
@@ -8631,7 +8753,7 @@
       </c>
       <c r="F33" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -8649,7 +8771,7 @@
       </c>
       <c r="F34" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>36</v>
       </c>
@@ -8667,7 +8789,7 @@
       </c>
       <c r="F35" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>60</v>
       </c>
@@ -8685,7 +8807,7 @@
       </c>
       <c r="F36" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>61</v>
       </c>
@@ -8703,7 +8825,7 @@
       </c>
       <c r="F37" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>44</v>
       </c>
@@ -8721,7 +8843,7 @@
       </c>
       <c r="F38" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
@@ -8739,7 +8861,7 @@
       </c>
       <c r="F39" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>63</v>
       </c>
@@ -8757,7 +8879,7 @@
       </c>
       <c r="F40" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>10</v>
       </c>
@@ -8775,7 +8897,7 @@
       </c>
       <c r="F41" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>49</v>
       </c>
@@ -8793,7 +8915,7 @@
       </c>
       <c r="F42" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>49</v>
       </c>
@@ -8811,7 +8933,7 @@
       </c>
       <c r="F43" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>52</v>
       </c>
@@ -8829,7 +8951,7 @@
       </c>
       <c r="F44" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>52</v>
       </c>
@@ -8847,7 +8969,7 @@
       </c>
       <c r="F45" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>53</v>
       </c>
@@ -8865,7 +8987,7 @@
       </c>
       <c r="F46" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>53</v>
       </c>
@@ -8883,7 +9005,7 @@
       </c>
       <c r="F47" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>53</v>
       </c>
@@ -8901,7 +9023,7 @@
       </c>
       <c r="F48" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>53</v>
       </c>
@@ -8919,7 +9041,7 @@
       </c>
       <c r="F49" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>57</v>
       </c>
@@ -8937,7 +9059,7 @@
       </c>
       <c r="F50" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>24</v>
       </c>
@@ -8955,7 +9077,7 @@
       </c>
       <c r="F51" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>58</v>
       </c>
@@ -8973,7 +9095,7 @@
       </c>
       <c r="F52" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>64</v>
       </c>
@@ -8991,7 +9113,7 @@
       </c>
       <c r="F53" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>65</v>
       </c>
@@ -9009,7 +9131,7 @@
       </c>
       <c r="F54" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+    <row r="55" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>31</v>
       </c>
@@ -9027,7 +9149,7 @@
       </c>
       <c r="F55" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row r="56" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>32</v>
       </c>
@@ -9045,7 +9167,7 @@
       </c>
       <c r="F56" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row r="57" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>35</v>
       </c>
@@ -9063,7 +9185,7 @@
       </c>
       <c r="F57" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row r="58" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>36</v>
       </c>
@@ -9081,7 +9203,7 @@
       </c>
       <c r="F58" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row r="59" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>66</v>
       </c>
@@ -9099,7 +9221,7 @@
       </c>
       <c r="F59" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+    <row r="60" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>41</v>
       </c>
@@ -9117,7 +9239,7 @@
       </c>
       <c r="F60" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row r="61" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>67</v>
       </c>
@@ -9135,7 +9257,7 @@
       </c>
       <c r="F61" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+    <row r="62" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>42</v>
       </c>
@@ -9153,7 +9275,7 @@
       </c>
       <c r="F62" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+    <row r="63" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>43</v>
       </c>
@@ -9171,7 +9293,7 @@
       </c>
       <c r="F63" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row r="64" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>68</v>
       </c>
@@ -9189,7 +9311,7 @@
       </c>
       <c r="F64" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row r="65" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>44</v>
       </c>
@@ -9207,7 +9329,7 @@
       </c>
       <c r="F65" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row r="66" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>69</v>
       </c>
@@ -9225,7 +9347,7 @@
       </c>
       <c r="F66" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row r="67" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>70</v>
       </c>
@@ -9243,7 +9365,7 @@
       </c>
       <c r="F67" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row r="68" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>6</v>
       </c>
@@ -9261,7 +9383,7 @@
       </c>
       <c r="F68" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+    <row r="69" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>49</v>
       </c>
@@ -9279,7 +9401,7 @@
       </c>
       <c r="F69" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row r="70" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>13</v>
       </c>
@@ -9297,7 +9419,7 @@
       </c>
       <c r="F70" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row r="71" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>53</v>
       </c>
@@ -9315,7 +9437,7 @@
       </c>
       <c r="F71" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row r="72" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>53</v>
       </c>
@@ -9333,7 +9455,7 @@
       </c>
       <c r="F72" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row r="73" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>14</v>
       </c>
@@ -9351,7 +9473,7 @@
       </c>
       <c r="F73" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row r="74" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>17</v>
       </c>
@@ -9369,7 +9491,7 @@
       </c>
       <c r="F74" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row r="75" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>23</v>
       </c>
@@ -9387,7 +9509,7 @@
       </c>
       <c r="F75" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row r="76" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>24</v>
       </c>
@@ -9405,7 +9527,7 @@
       </c>
       <c r="F76" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row r="77" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>30</v>
       </c>
@@ -9423,7 +9545,7 @@
       </c>
       <c r="F77" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row r="78" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>65</v>
       </c>
@@ -9441,7 +9563,7 @@
       </c>
       <c r="F78" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row r="79" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>31</v>
       </c>
@@ -9459,7 +9581,7 @@
       </c>
       <c r="F79" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row r="80" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>72</v>
       </c>
@@ -9477,7 +9599,7 @@
       </c>
       <c r="F80" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row r="81" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>66</v>
       </c>
@@ -9495,7 +9617,7 @@
       </c>
       <c r="F81" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row r="82" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>41</v>
       </c>
@@ -9513,7 +9635,7 @@
       </c>
       <c r="F82" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+    <row r="83" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>67</v>
       </c>
@@ -9531,7 +9653,7 @@
       </c>
       <c r="F83" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+    <row r="84" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>42</v>
       </c>
@@ -9549,7 +9671,7 @@
       </c>
       <c r="F84" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+    <row r="85" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>44</v>
       </c>
@@ -9567,7 +9689,7 @@
       </c>
       <c r="F85" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+    <row r="86" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>69</v>
       </c>
@@ -9585,7 +9707,7 @@
       </c>
       <c r="F86" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+    <row r="87" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>70</v>
       </c>
@@ -9603,7 +9725,7 @@
       </c>
       <c r="F87" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+    <row r="88" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>63</v>
       </c>
@@ -9621,7 +9743,7 @@
       </c>
       <c r="F88" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+    <row r="89" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>49</v>
       </c>
@@ -9639,7 +9761,7 @@
       </c>
       <c r="F89" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+    <row r="90" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>52</v>
       </c>
@@ -9657,7 +9779,7 @@
       </c>
       <c r="F90" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+    <row r="91" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>52</v>
       </c>
@@ -9675,7 +9797,7 @@
       </c>
       <c r="F91" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+    <row r="92" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>53</v>
       </c>
@@ -9693,7 +9815,7 @@
       </c>
       <c r="F92" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+    <row r="93" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>53</v>
       </c>
@@ -9711,7 +9833,7 @@
       </c>
       <c r="F93" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+    <row r="94" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>17</v>
       </c>
@@ -9729,7 +9851,7 @@
       </c>
       <c r="F94" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+    <row r="95" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>74</v>
       </c>
@@ -9747,7 +9869,7 @@
       </c>
       <c r="F95" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+    <row r="96" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>56</v>
       </c>
@@ -9765,7 +9887,7 @@
       </c>
       <c r="F96" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+    <row r="97" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>57</v>
       </c>
@@ -9783,7 +9905,7 @@
       </c>
       <c r="F97" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+    <row r="98" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>24</v>
       </c>
@@ -9801,7 +9923,7 @@
       </c>
       <c r="F98" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+    <row r="99" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>58</v>
       </c>
@@ -9819,7 +9941,7 @@
       </c>
       <c r="F99" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+    <row r="100" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>75</v>
       </c>
@@ -9837,7 +9959,7 @@
       </c>
       <c r="F100" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+    <row r="101" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>32</v>
       </c>
@@ -9855,7 +9977,7 @@
       </c>
       <c r="F101" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
+    <row r="102" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>36</v>
       </c>
@@ -9873,7 +9995,7 @@
       </c>
       <c r="F102" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+    <row r="103" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>76</v>
       </c>
@@ -9891,7 +10013,7 @@
       </c>
       <c r="F103" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
+    <row r="104" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>77</v>
       </c>
@@ -9909,7 +10031,7 @@
       </c>
       <c r="F104" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
+    <row r="105" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>78</v>
       </c>
@@ -9927,7 +10049,7 @@
       </c>
       <c r="F105" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
+    <row r="106" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>79</v>
       </c>
@@ -9945,7 +10067,7 @@
       </c>
       <c r="F106" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
+    <row r="107" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>6</v>
       </c>
@@ -9963,7 +10085,7 @@
       </c>
       <c r="F107" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
+    <row r="108" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>63</v>
       </c>
@@ -9981,7 +10103,7 @@
       </c>
       <c r="F108" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
+    <row r="109" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>10</v>
       </c>
@@ -9999,7 +10121,7 @@
       </c>
       <c r="F109" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
+    <row r="110" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>49</v>
       </c>
@@ -10017,7 +10139,7 @@
       </c>
       <c r="F110" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
+    <row r="111" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>52</v>
       </c>
@@ -10035,7 +10157,7 @@
       </c>
       <c r="F111" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
+    <row r="112" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>52</v>
       </c>
@@ -10053,7 +10175,7 @@
       </c>
       <c r="F112" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
+    <row r="113" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>53</v>
       </c>
@@ -10071,7 +10193,7 @@
       </c>
       <c r="F113" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
+    <row r="114" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>53</v>
       </c>
@@ -10089,7 +10211,7 @@
       </c>
       <c r="F114" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
+    <row r="115" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>53</v>
       </c>
@@ -10107,7 +10229,7 @@
       </c>
       <c r="F115" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
+    <row r="116" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>57</v>
       </c>
@@ -10125,7 +10247,7 @@
       </c>
       <c r="F116" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
+    <row r="117" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>24</v>
       </c>
@@ -10143,7 +10265,7 @@
       </c>
       <c r="F117" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
+    <row r="118" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>58</v>
       </c>
@@ -10161,7 +10283,7 @@
       </c>
       <c r="F118" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
+    <row r="119" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>59</v>
       </c>
@@ -10179,7 +10301,7 @@
       </c>
       <c r="F119" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
+    <row r="120" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>64</v>
       </c>
@@ -10197,7 +10319,7 @@
       </c>
       <c r="F120" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
+    <row r="121" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>32</v>
       </c>
@@ -10215,7 +10337,7 @@
       </c>
       <c r="F121" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
+    <row r="122" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>35</v>
       </c>
@@ -10233,7 +10355,7 @@
       </c>
       <c r="F122" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
+    <row r="123" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>36</v>
       </c>
@@ -10251,7 +10373,7 @@
       </c>
       <c r="F123" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
+    <row r="124" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>76</v>
       </c>
@@ -10269,7 +10391,7 @@
       </c>
       <c r="F124" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
+    <row r="125" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>81</v>
       </c>
@@ -10287,7 +10409,7 @@
       </c>
       <c r="F125" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
+    <row r="126" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>77</v>
       </c>
@@ -10305,7 +10427,7 @@
       </c>
       <c r="F126" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
+    <row r="127" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>78</v>
       </c>
@@ -10323,7 +10445,7 @@
       </c>
       <c r="F127" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
+    <row r="128" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>79</v>
       </c>
@@ -10341,7 +10463,7 @@
       </c>
       <c r="F128" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
+    <row r="129" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>82</v>
       </c>
@@ -10359,7 +10481,7 @@
       </c>
       <c r="F129" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
+    <row r="130" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>6</v>
       </c>
@@ -10377,7 +10499,7 @@
       </c>
       <c r="F130" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
+    <row r="131" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>63</v>
       </c>
@@ -10395,7 +10517,7 @@
       </c>
       <c r="F131" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
+    <row r="132" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>10</v>
       </c>
@@ -10413,7 +10535,7 @@
       </c>
       <c r="F132" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
+    <row r="133" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>52</v>
       </c>
@@ -10431,7 +10553,7 @@
       </c>
       <c r="F133" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
+    <row r="134" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>52</v>
       </c>
@@ -10449,7 +10571,7 @@
       </c>
       <c r="F134" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
+    <row r="135" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>53</v>
       </c>
@@ -10467,7 +10589,7 @@
       </c>
       <c r="F135" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
+    <row r="136" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>53</v>
       </c>
@@ -10485,7 +10607,7 @@
       </c>
       <c r="F136" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
+    <row r="137" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>53</v>
       </c>
@@ -10503,7 +10625,7 @@
       </c>
       <c r="F137" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
+    <row r="138" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>84</v>
       </c>
@@ -10521,7 +10643,7 @@
       </c>
       <c r="F138" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
+    <row r="139" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>85</v>
       </c>
@@ -10539,7 +10661,7 @@
       </c>
       <c r="F139" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
+    <row r="140" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>57</v>
       </c>
@@ -10557,7 +10679,7 @@
       </c>
       <c r="F140" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
+    <row r="141" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>24</v>
       </c>
@@ -10575,7 +10697,7 @@
       </c>
       <c r="F141" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
+    <row r="142" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>58</v>
       </c>
@@ -10593,7 +10715,7 @@
       </c>
       <c r="F142" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
+    <row r="143" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>59</v>
       </c>
@@ -10611,7 +10733,7 @@
       </c>
       <c r="F143" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
+    <row r="144" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>64</v>
       </c>
@@ -10629,7 +10751,7 @@
       </c>
       <c r="F144" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
+    <row r="145" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>32</v>
       </c>
@@ -10647,7 +10769,7 @@
       </c>
       <c r="F145" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
+    <row r="146" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>35</v>
       </c>
@@ -10665,7 +10787,7 @@
       </c>
       <c r="F146" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
+    <row r="147" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>36</v>
       </c>
@@ -10683,7 +10805,7 @@
       </c>
       <c r="F147" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
+    <row r="148" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>76</v>
       </c>
@@ -10701,7 +10823,7 @@
       </c>
       <c r="F148" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
+    <row r="149" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>81</v>
       </c>
@@ -10719,7 +10841,7 @@
       </c>
       <c r="F149" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
+    <row r="150" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>77</v>
       </c>
@@ -10737,7 +10859,7 @@
       </c>
       <c r="F150" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
+    <row r="151" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>86</v>
       </c>
@@ -10755,7 +10877,7 @@
       </c>
       <c r="F151" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
+    <row r="152" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>63</v>
       </c>
@@ -10773,7 +10895,7 @@
       </c>
       <c r="F152" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
+    <row r="153" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>10</v>
       </c>
@@ -10791,7 +10913,7 @@
       </c>
       <c r="F153" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
+    <row r="154" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>88</v>
       </c>
@@ -10809,7 +10931,7 @@
       </c>
       <c r="F154" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
+    <row r="155" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>89</v>
       </c>
@@ -10827,7 +10949,7 @@
       </c>
       <c r="F155" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
+    <row r="156" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>49</v>
       </c>
@@ -10845,7 +10967,7 @@
       </c>
       <c r="F156" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
+    <row r="157" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>52</v>
       </c>
@@ -10863,7 +10985,7 @@
       </c>
       <c r="F157" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
+    <row r="158" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>52</v>
       </c>
@@ -10881,7 +11003,7 @@
       </c>
       <c r="F158" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
+    <row r="159" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>53</v>
       </c>
@@ -10899,7 +11021,7 @@
       </c>
       <c r="F159" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
+    <row r="160" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>53</v>
       </c>
@@ -10917,7 +11039,7 @@
       </c>
       <c r="F160" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
+    <row r="161" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>53</v>
       </c>
@@ -10935,7 +11057,7 @@
       </c>
       <c r="F161" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
+    <row r="162" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>17</v>
       </c>
@@ -10953,7 +11075,7 @@
       </c>
       <c r="F162" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
+    <row r="163" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>90</v>
       </c>
@@ -10971,7 +11093,7 @@
       </c>
       <c r="F163" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
+    <row r="164" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>91</v>
       </c>
@@ -10989,7 +11111,7 @@
       </c>
       <c r="F164" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
+    <row r="165" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>92</v>
       </c>
@@ -11007,7 +11129,7 @@
       </c>
       <c r="F165" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
+    <row r="166" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>93</v>
       </c>
@@ -11025,7 +11147,7 @@
       </c>
       <c r="F166" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
+    <row r="167" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>20</v>
       </c>
@@ -11043,7 +11165,7 @@
       </c>
       <c r="F167" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
+    <row r="168" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>57</v>
       </c>
@@ -11061,7 +11183,7 @@
       </c>
       <c r="F168" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
+    <row r="169" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>94</v>
       </c>
@@ -11079,7 +11201,7 @@
       </c>
       <c r="F169" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
+    <row r="170" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>24</v>
       </c>
@@ -11097,7 +11219,7 @@
       </c>
       <c r="F170" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
+    <row r="171" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>58</v>
       </c>
@@ -11115,7 +11237,7 @@
       </c>
       <c r="F171" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
+    <row r="172" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>59</v>
       </c>
@@ -11133,7 +11255,7 @@
       </c>
       <c r="F172" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
+    <row r="173" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>97</v>
       </c>
@@ -11151,7 +11273,7 @@
       </c>
       <c r="F173" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
+    <row r="174" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>64</v>
       </c>
@@ -11169,7 +11291,7 @@
       </c>
       <c r="F174" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
+    <row r="175" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>65</v>
       </c>
@@ -11187,7 +11309,7 @@
       </c>
       <c r="F175" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
+    <row r="176" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>32</v>
       </c>
@@ -11205,7 +11327,7 @@
       </c>
       <c r="F176" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75">
+    <row r="177" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>35</v>
       </c>
@@ -11223,7 +11345,7 @@
       </c>
       <c r="F177" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75">
+    <row r="178" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>36</v>
       </c>
@@ -11241,7 +11363,7 @@
       </c>
       <c r="F178" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75">
+    <row r="179" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>98</v>
       </c>
@@ -11259,7 +11381,7 @@
       </c>
       <c r="F179" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75">
+    <row r="180" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>70</v>
       </c>
@@ -11277,7 +11399,7 @@
       </c>
       <c r="F180" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75">
+    <row r="181" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>77</v>
       </c>
@@ -11295,7 +11417,7 @@
       </c>
       <c r="F181" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75">
+    <row r="182" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>86</v>
       </c>
@@ -11313,7 +11435,7 @@
       </c>
       <c r="F182" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75">
+    <row r="183" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>78</v>
       </c>
@@ -11331,7 +11453,7 @@
       </c>
       <c r="F183" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75">
+    <row r="184" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>79</v>
       </c>
@@ -11349,7 +11471,7 @@
       </c>
       <c r="F184" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75">
+    <row r="185" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>63</v>
       </c>
@@ -11367,7 +11489,7 @@
       </c>
       <c r="F185" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75">
+    <row r="186" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>10</v>
       </c>
@@ -11385,7 +11507,7 @@
       </c>
       <c r="F186" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75">
+    <row r="187" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>88</v>
       </c>
@@ -11403,7 +11525,7 @@
       </c>
       <c r="F187" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75">
+    <row r="188" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>100</v>
       </c>
@@ -11421,7 +11543,7 @@
       </c>
       <c r="F188" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75">
+    <row r="189" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>89</v>
       </c>
@@ -11439,7 +11561,7 @@
       </c>
       <c r="F189" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75">
+    <row r="190" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>53</v>
       </c>
@@ -11457,7 +11579,7 @@
       </c>
       <c r="F190" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75">
+    <row r="191" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>92</v>
       </c>
@@ -11475,7 +11597,7 @@
       </c>
       <c r="F191" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75">
+    <row r="192" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>93</v>
       </c>
@@ -11493,7 +11615,7 @@
       </c>
       <c r="F192" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75">
+    <row r="193" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>20</v>
       </c>
@@ -11511,7 +11633,7 @@
       </c>
       <c r="F193" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75">
+    <row r="194" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>94</v>
       </c>
@@ -11529,7 +11651,7 @@
       </c>
       <c r="F194" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75">
+    <row r="195" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>24</v>
       </c>
@@ -11547,7 +11669,7 @@
       </c>
       <c r="F195" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75">
+    <row r="196" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>59</v>
       </c>
@@ -11565,7 +11687,7 @@
       </c>
       <c r="F196" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75">
+    <row r="197" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>64</v>
       </c>
@@ -11583,7 +11705,7 @@
       </c>
       <c r="F197" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75">
+    <row r="198" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>65</v>
       </c>
@@ -11601,7 +11723,7 @@
       </c>
       <c r="F198" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75">
+    <row r="199" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>32</v>
       </c>
@@ -11619,7 +11741,7 @@
       </c>
       <c r="F199" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75">
+    <row r="200" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>35</v>
       </c>
@@ -11637,7 +11759,7 @@
       </c>
       <c r="F200" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75">
+    <row r="201" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>36</v>
       </c>
@@ -11655,7 +11777,7 @@
       </c>
       <c r="F201" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75">
+    <row r="202" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>101</v>
       </c>
@@ -11673,7 +11795,7 @@
       </c>
       <c r="F202" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75">
+    <row r="203" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>98</v>
       </c>
@@ -11691,7 +11813,7 @@
       </c>
       <c r="F203" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="18.75">
+    <row r="204" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>44</v>
       </c>
@@ -11709,7 +11831,7 @@
       </c>
       <c r="F204" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="18.75">
+    <row r="205" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>45</v>
       </c>
@@ -11727,7 +11849,7 @@
       </c>
       <c r="F205" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="18.75">
+    <row r="206" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>77</v>
       </c>
@@ -11745,7 +11867,7 @@
       </c>
       <c r="F206" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="18.75">
+    <row r="207" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>86</v>
       </c>
@@ -11763,7 +11885,7 @@
       </c>
       <c r="F207" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="18.75">
+    <row r="208" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>78</v>
       </c>
@@ -11781,7 +11903,7 @@
       </c>
       <c r="F208" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="18.75">
+    <row r="209" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>79</v>
       </c>
@@ -11799,7 +11921,7 @@
       </c>
       <c r="F209" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="18.75">
+    <row r="210" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>102</v>
       </c>
@@ -11817,7 +11939,7 @@
       </c>
       <c r="F210" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="18.75">
+    <row r="211" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>10</v>
       </c>
@@ -11835,7 +11957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="18.75">
+    <row r="212" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>88</v>
       </c>
@@ -11853,7 +11975,7 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="18.75">
+    <row r="213" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>104</v>
       </c>
@@ -11871,7 +11993,7 @@
         <v>104</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="18.75">
+    <row r="214" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>53</v>
       </c>
@@ -11889,7 +12011,7 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="18.75">
+    <row r="215" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>53</v>
       </c>
@@ -11907,7 +12029,7 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="18.75">
+    <row r="216" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>53</v>
       </c>
@@ -11925,7 +12047,7 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="18.75">
+    <row r="217" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>53</v>
       </c>
@@ -11943,7 +12065,7 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="18.75">
+    <row r="218" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>14</v>
       </c>
@@ -11961,7 +12083,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="18.75">
+    <row r="219" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>105</v>
       </c>
@@ -11979,7 +12101,7 @@
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="18.75">
+    <row r="220" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>31</v>
       </c>
@@ -11997,7 +12119,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="18.75">
+    <row r="221" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>35</v>
       </c>
@@ -12015,7 +12137,7 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="18.75">
+    <row r="222" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>36</v>
       </c>
@@ -12033,7 +12155,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="18.75">
+    <row r="223" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>106</v>
       </c>
@@ -12051,7 +12173,7 @@
         <v>106</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="18.75">
+    <row r="224" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>98</v>
       </c>
@@ -12069,7 +12191,7 @@
         <v>98</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="18.75">
+    <row r="225" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>107</v>
       </c>
@@ -12087,7 +12209,7 @@
         <v>107</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="18.75">
+    <row r="226" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>108</v>
       </c>
@@ -12105,7 +12227,7 @@
         <v>108</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="18.75">
+    <row r="227" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>109</v>
       </c>
@@ -12123,7 +12245,7 @@
         <v>109</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="18.75">
+    <row r="228" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>110</v>
       </c>
@@ -12141,7 +12263,7 @@
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="18.75">
+    <row r="229" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>111</v>
       </c>
@@ -12159,7 +12281,7 @@
         <v>111</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="18.75">
+    <row r="230" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>112</v>
       </c>
@@ -12177,7 +12299,7 @@
         <v>112</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="18.75">
+    <row r="231" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>113</v>
       </c>
@@ -12195,7 +12317,7 @@
         <v>113</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="18.75">
+    <row r="232" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>114</v>
       </c>
@@ -12213,7 +12335,7 @@
         <v>114</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="18.75">
+    <row r="233" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>115</v>
       </c>
@@ -12231,7 +12353,7 @@
         <v>115</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="18.75">
+    <row r="234" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>10</v>
       </c>
@@ -12249,7 +12371,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="18.75">
+    <row r="235" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>49</v>
       </c>
@@ -12267,7 +12389,7 @@
         <v>49</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="18.75">
+    <row r="236" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>53</v>
       </c>
@@ -12285,7 +12407,7 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="18.75">
+    <row r="237" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>53</v>
       </c>
@@ -12303,7 +12425,7 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="18.75">
+    <row r="238" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>53</v>
       </c>
@@ -12321,7 +12443,7 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="18.75">
+    <row r="239" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>17</v>
       </c>
@@ -12339,7 +12461,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="18.75">
+    <row r="240" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>20</v>
       </c>
@@ -12357,7 +12479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="18.75">
+    <row r="241" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>23</v>
       </c>
@@ -12375,7 +12497,7 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="18.75">
+    <row r="242" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>117</v>
       </c>
@@ -12393,7 +12515,7 @@
         <v>117</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="18.75">
+    <row r="243" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>118</v>
       </c>
@@ -12411,7 +12533,7 @@
         <v>118</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="18.75">
+    <row r="244" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>105</v>
       </c>
@@ -12429,7 +12551,7 @@
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="18.75">
+    <row r="245" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>119</v>
       </c>
@@ -12447,7 +12569,7 @@
         <v>119</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="18.75">
+    <row r="246" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>31</v>
       </c>
@@ -12465,7 +12587,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="18.75">
+    <row r="247" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>35</v>
       </c>
@@ -12483,7 +12605,7 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="18.75">
+    <row r="248" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>36</v>
       </c>
@@ -12501,7 +12623,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="18.75">
+    <row r="249" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>120</v>
       </c>
@@ -12519,7 +12641,7 @@
         <v>120</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="18.75">
+    <row r="250" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>106</v>
       </c>
@@ -12537,7 +12659,7 @@
         <v>106</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="18.75">
+    <row r="251" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>121</v>
       </c>
@@ -12555,7 +12677,7 @@
         <v>121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="18.75">
+    <row r="252" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>122</v>
       </c>
@@ -12573,7 +12695,7 @@
         <v>122</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="18.75">
+    <row r="253" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>123</v>
       </c>
@@ -12591,7 +12713,7 @@
         <v>123</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="18.75">
+    <row r="254" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>124</v>
       </c>
@@ -12609,7 +12731,7 @@
         <v>124</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="18.75">
+    <row r="255" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>98</v>
       </c>
@@ -12627,7 +12749,7 @@
         <v>98</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="18.75">
+    <row r="256" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>107</v>
       </c>
@@ -12645,7 +12767,7 @@
         <v>107</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="18.75">
+    <row r="257" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>70</v>
       </c>
@@ -12663,7 +12785,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="18.75">
+    <row r="258" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>10</v>
       </c>
@@ -12681,7 +12803,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="18.75">
+    <row r="259" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>104</v>
       </c>
@@ -12699,7 +12821,7 @@
         <v>104</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="18.75">
+    <row r="260" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>126</v>
       </c>
@@ -12717,7 +12839,7 @@
         <v>126</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="18.75">
+    <row r="261" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>49</v>
       </c>
@@ -12735,7 +12857,7 @@
         <v>49</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="18.75">
+    <row r="262" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>13</v>
       </c>
@@ -12753,7 +12875,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="18.75">
+    <row r="263" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>127</v>
       </c>
@@ -12771,7 +12893,7 @@
         <v>127</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="18.75">
+    <row r="264" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>53</v>
       </c>
@@ -12789,7 +12911,7 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="18.75">
+    <row r="265" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>14</v>
       </c>
@@ -12807,7 +12929,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="18.75">
+    <row r="266" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>20</v>
       </c>
@@ -12825,7 +12947,7 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="18.75">
+    <row r="267" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>23</v>
       </c>
@@ -12843,7 +12965,7 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="18.75">
+    <row r="268" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>105</v>
       </c>
@@ -12861,7 +12983,7 @@
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="18.75">
+    <row r="269" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>128</v>
       </c>
@@ -12879,7 +13001,7 @@
         <v>128</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="18.75">
+    <row r="270" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>31</v>
       </c>
@@ -12897,7 +13019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="18.75">
+    <row r="271" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>35</v>
       </c>
@@ -12915,7 +13037,7 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="18.75">
+    <row r="272" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>36</v>
       </c>
@@ -12933,7 +13055,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="18.75">
+    <row r="273" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>120</v>
       </c>
@@ -12951,7 +13073,7 @@
         <v>120</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="18.75">
+    <row r="274" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>106</v>
       </c>
@@ -12969,7 +13091,7 @@
         <v>106</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="18.75">
+    <row r="275" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>122</v>
       </c>
@@ -12987,7 +13109,7 @@
         <v>122</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="18.75">
+    <row r="276" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>123</v>
       </c>
@@ -13005,7 +13127,7 @@
         <v>123</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="18.75">
+    <row r="277" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>129</v>
       </c>
@@ -13023,7 +13145,7 @@
         <v>129</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="18.75">
+    <row r="278" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>130</v>
       </c>
@@ -13041,7 +13163,7 @@
         <v>130</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="18.75">
+    <row r="279" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>131</v>
       </c>
@@ -13059,7 +13181,7 @@
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="18.75">
+    <row r="280" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>132</v>
       </c>
@@ -13077,7 +13199,7 @@
         <v>132</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="18.75">
+    <row r="281" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>98</v>
       </c>
@@ -13095,7 +13217,7 @@
         <v>98</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="18.75">
+    <row r="282" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>107</v>
       </c>
@@ -13113,7 +13235,7 @@
         <v>107</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="18.75">
+    <row r="283" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>70</v>
       </c>
@@ -13134,4 +13256,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{725ca717-11da-4935-b601-f527b9741f2e}" enabled="1" method="Standard" siteId="{d852d5cd-724c-4128-8812-ffa5db3f8507}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Map Opeperation/tb_de_para.xlsx
+++ b/Map Opeperation/tb_de_para.xlsx
@@ -3075,7 +3075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3103,148 +3103,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ELT(BSG12)</t>
+          <t>KW(125)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TIPO ELETTRIFICAZIONE</t>
+          <t>Potenza max KW</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Maximum power kW</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MHEV</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KW(125)</t>
+          <t>L(L11)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Potenza max KW</t>
+          <t>Livello Allestimento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maximum power kW</t>
+          <t>Trim Level</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>LL5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L(L11)</t>
+          <t>M(00)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Livello Allestimento</t>
+          <t>Marchio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trim Level</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LL5</t>
-        </is>
-      </c>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M(00)</t>
+          <t>T(ASP)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marchio</t>
+          <t>Caratteristiche Motore</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Engine Features</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sovralimentato Turbo</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T(ASP)</t>
+          <t>TC(PKDC)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caratteristiche Motore</t>
+          <t>Numero Porte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Engine Features</t>
+          <t>Number of doors</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sovralimentato Turbo</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC(PKDC)</t>
+          <t>TT(4X2)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Numero Porte</t>
+          <t>Tipo Trazione</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Number of doors</t>
+          <t>Traction type</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TT(4X2)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Tipo Trazione</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Traction type</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
         <is>
           <t>FWD</t>
         </is>
